--- a/output/pdf_financials_xlsx/VERT.xlsx
+++ b/output/pdf_financials_xlsx/VERT.xlsx
@@ -6273,46 +6273,46 @@
         <v>1.026279</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.182946</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.19624</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.203285</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.203285</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.203285</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.270816</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.595826</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.655226</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.679974</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.141815</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.252315</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.520715</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.564815</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>2.588515</v>
       </c>
     </row>
     <row r="93">
@@ -7838,31 +7838,31 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.8423349999999999</v>
+        <v>0.19905</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.10019</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.183129</v>
+        <v>-0.108084</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.519033</v>
+        <v>1.501463</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002693</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.324132</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.070592</v>
+        <v>-0.382353</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.259688</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>-0.334022</v>
@@ -9958,7 +9958,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -11780,7 +11784,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12418,7 +12426,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -13054,7 +13066,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -13586,7 +13602,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14224,7 +14244,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -20548,7 +20572,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -22322,7 +22350,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -24222,7 +24254,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VERT.xlsx
+++ b/output/pdf_financials_xlsx/VERT.xlsx
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.005208</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>8.6e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.001187</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.279265</v>
+        <v>-0.284473</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.185718</v>
+        <v>-0.185804</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.868101</v>
+        <v>-0.8692879999999999</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.038427</v>
@@ -2192,13 +2192,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.279265</v>
+        <v>-0.284473</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.185718</v>
+        <v>-0.185804</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.868101</v>
+        <v>-0.8692879999999999</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.038427</v>
@@ -2515,7 +2515,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.360223</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.007254</v>
@@ -2527,46 +2527,46 @@
         <v>0.02049</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005372</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005837</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.167751</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.414852</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.003397</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.08591799999999999</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.650962</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.005737</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.293253</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.024378</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.045398</v>
       </c>
     </row>
     <row r="35">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.360223</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.007254</v>
@@ -2649,46 +2649,46 @@
         <v>0.02049</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.005372</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000113</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000648</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.0225</v>
+        <v>0.022505</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005837</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.167751</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.414852</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.003397</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.08591799999999999</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.650962</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.005737</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.293253</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.024378</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.045398</v>
       </c>
     </row>
     <row r="37">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.381441</v>
+        <v>0.021218</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.001127</v>
@@ -3381,46 +3381,46 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.027565</v>
+        <v>0.022193</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008706999999999999</v>
+        <v>0.008593999999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.004534</v>
+        <v>0.003886</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.01377</v>
+        <v>0.013765</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.024751</v>
+        <v>0.018914</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.182498</v>
+        <v>0.014747</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.451156</v>
+        <v>0.036304</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.010239</v>
+        <v>0.006842</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.095488</v>
+        <v>0.00957</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.712829</v>
+        <v>0.061867</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.012018</v>
+        <v>0.006281</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.31053</v>
+        <v>0.017277</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.033036</v>
+        <v>0.008658000000000001</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.048264</v>
+        <v>0.002866</v>
       </c>
     </row>
     <row r="49">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -51290,7 +51290,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -53004,7 +53004,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E423" s="5" t="n">

--- a/output/pdf_financials_xlsx/VERT.xlsx
+++ b/output/pdf_financials_xlsx/VERT.xlsx
@@ -1364,7 +1364,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.044034</v>
+        <v>-0.044034</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -4498,10 +4498,10 @@
         <v>0</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.361523</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>0.666382</v>
       </c>
       <c r="S64" s="3" t="n">
         <v>0</v>
@@ -4660,34 +4660,34 @@
         <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.244</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.203</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.164</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.145</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.145705</v>
       </c>
       <c r="S67" s="3" t="n">
-        <v>0</v>
+        <v>0.042665</v>
       </c>
     </row>
     <row r="68">
@@ -6834,16 +6834,16 @@
         <v>0</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.007035</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>0.049471</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>0.003844</v>
       </c>
       <c r="S101" s="3" t="n">
-        <v>0</v>
+        <v>0.007161</v>
       </c>
     </row>
     <row r="102">
@@ -7386,13 +7386,13 @@
         <v>0</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.001889</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.001911</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.001934</v>
       </c>
     </row>
     <row r="111">
@@ -7670,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.07761999999999999</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -16564,7 +16564,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16864,7 +16868,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -17410,7 +17418,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -19634,7 +19646,11 @@
           <t>Private Placement</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -19940,7 +19956,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -21718,7 +21738,11 @@
           <t>Proceeds from sales of marketable securities</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -23088,7 +23112,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -23826,7 +23854,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -28192,7 +28224,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E186" s="5" t="n">
         <v>-0.044034</v>
       </c>
@@ -55016,7 +55052,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E442" s="5" t="n">
         <v>0.044034</v>
       </c>
